--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">

--- a/output/za.xlsx
+++ b/output/za.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
